--- a/Test Cases/Test_Cases_Report.xlsx
+++ b/Test Cases/Test_Cases_Report.xlsx
@@ -851,7 +851,7 @@
       <c r="G3" s="7" t="inlineStr">
         <is>
           <t>{
-  "email": "theknightahmedgaber@gmail.com",
+  "email": "admin@example.com",
   "password": "admin_password"
 }</t>
         </is>
@@ -860,7 +860,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/Login
+3. URL: {{base_url}}api/Accounts/Login
 4. Add credentials in body
 5. Click Send</t>
         </is>
@@ -938,7 +938,7 @@
       <c r="G4" s="14" t="inlineStr">
         <is>
           <t>{
-  "email": "theknightahmedgaber@gmail.com",
+  "email": "admin@example.com",
   "password": "admin_password"
 }</t>
         </is>
@@ -947,7 +947,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/Login
+3. URL: {{base_url}}api/Accounts/Login
 4. Add credentials in body
 5. Click Send</t>
         </is>
@@ -1025,7 +1025,7 @@
       <c r="G5" s="7" t="inlineStr">
         <is>
           <t>{
-  "email": "theknightahmedgaber@gmail.com",
+  "email": "admin@example.com",
   "password": "admin_password"
 }</t>
         </is>
@@ -1034,7 +1034,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/Login
+3. URL: {{base_url}}api/Accounts/Login
 4. Add credentials in body
 5. Click Send</t>
         </is>
@@ -1112,7 +1112,7 @@
       <c r="G6" s="14" t="inlineStr">
         <is>
           <t>{
-  "email": "theknightahmedgaber@gmail.com",
+  "email": "admin@example.com",
   "password": "admin_password"
 }</t>
         </is>
@@ -1121,7 +1121,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/Login
+3. URL: {{base_url}}api/Accounts/Login
 4. Add credentials in body
 5. Click Send</t>
         </is>
@@ -1199,7 +1199,7 @@
       <c r="G7" s="7" t="inlineStr">
         <is>
           <t>{
-  "email": "theknightahmedgaber@gmail.com",
+  "email": "admin@example.com",
   "password": "admin_password"
 }</t>
         </is>
@@ -1208,7 +1208,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/Login
+3. URL: {{base_url}}api/Accounts/Login
 4. Add credentials in body
 5. Click Send</t>
         </is>
@@ -1286,7 +1286,7 @@
       <c r="G8" s="14" t="inlineStr">
         <is>
           <t>{
-  "email": "theknightahmedgaber@gmail.com",
+  "email": "admin@example.com",
   "password": "admin_password"
 }</t>
         </is>
@@ -1295,7 +1295,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/Login
+3. URL: {{base_url}}api/Accounts/Login
 4. Add credentials in body
 5. Click Send</t>
         </is>
@@ -1373,7 +1373,7 @@
       <c r="G9" s="7" t="inlineStr">
         <is>
           <t>{
-  "email": "theknightahmedgaber@gmail.com",
+  "email": "admin@example.com",
   "password": "admin_password"
 }</t>
         </is>
@@ -1382,7 +1382,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/Login
+3. URL: {{base_url}}api/Accounts/Login
 4. Add credentials in body
 5. Click Send</t>
         </is>
@@ -1460,7 +1460,7 @@
       <c r="G10" s="14" t="inlineStr">
         <is>
           <t>{
-  "email": "theknightahmedgaber@gmail.com",
+  "email": "admin@example.com",
   "password": "admin_password"
 }</t>
         </is>
@@ -1469,7 +1469,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/Login
+3. URL: {{base_url}}api/Accounts/Login
 4. Add credentials in body
 5. Click Send</t>
         </is>
@@ -1546,7 +1546,7 @@
       <c r="G11" s="7" t="inlineStr">
         <is>
           <t>{
-  "email": "theknightahmedgaber@gmail.com",
+  "email": "admin@example.com",
   "password": "wrongpassword123"
 }</t>
         </is>
@@ -1555,7 +1555,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/Login
+3. URL: {{base_url}}api/Accounts/Login
 4. Enter wrong password
 5. Click Send</t>
         </is>
@@ -1632,7 +1632,7 @@
       <c r="G12" s="14" t="inlineStr">
         <is>
           <t>{
-  "email": "theknightahmedgaber@gmail.com",
+  "email": "admin@example.com",
   "password": "wrongpassword123"
 }</t>
         </is>
@@ -1641,7 +1641,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/Login
+3. URL: {{base_url}}api/Accounts/Login
 4. Enter wrong password
 5. Click Send</t>
         </is>
@@ -1718,7 +1718,7 @@
       <c r="G13" s="7" t="inlineStr">
         <is>
           <t>{
-  "email": "theknightahmedgaber@gmail.com",
+  "email": "admin@example.com",
   "password": "wrongpassword123"
 }</t>
         </is>
@@ -1727,7 +1727,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/Login
+3. URL: {{base_url}}api/Accounts/Login
 4. Enter wrong password
 5. Click Send</t>
         </is>
@@ -1804,7 +1804,7 @@
       <c r="G14" s="14" t="inlineStr">
         <is>
           <t>{
-  "email": "theknightahmedgaber@gmail.com",
+  "email": "admin@example.com",
   "password": "wrongpassword123"
 }</t>
         </is>
@@ -1813,7 +1813,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/Login
+3. URL: {{base_url}}api/Accounts/Login
 4. Enter wrong password
 5. Click Send</t>
         </is>
@@ -1922,7 +1922,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Courses/CreateCourse
+3. URL: {{base_url}}api/Courses/CreateCourse
 4. Set Authorization: Bearer {{admin_token}}
 5. Set Body as form-data with course data
 6. Click Send</t>
@@ -2011,7 +2011,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Courses/CreateCourse
+3. URL: {{base_url}}api/Courses/CreateCourse
 4. Set Authorization: Bearer {{admin_token}}
 5. Set Body as form-data with course data
 6. Click Send</t>
@@ -2100,7 +2100,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Courses/CreateCourse
+3. URL: {{base_url}}api/Courses/CreateCourse
 4. Set Authorization: Bearer {{admin_token}}
 5. Set Body as form-data with course data
 6. Click Send</t>
@@ -2177,14 +2177,14 @@
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Course ID: {{PythonCourse_id}}</t>
+          <t>Course ID: {{python_course_id}}</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
           <t>1. Open Postman
 2. Set method to GET
-3. URL: {{Base_url}}api/Courses/GetCourseById/{{PythonCourse_id}}
+3. URL: {{base_url}}api/Courses/GetCourseById/{{python_course_id}}
 4. Set Authorization: Bearer {{admin_token}}
 5. Click Send</t>
         </is>
@@ -2260,14 +2260,14 @@
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>Course ID: {{PythonCourse_id}}</t>
+          <t>Course ID: {{python_course_id}}</t>
         </is>
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
           <t>1. Open Postman
 2. Set method to GET
-3. URL: {{Base_url}}api/Courses/GetCourseById/{{PythonCourse_id}}
+3. URL: {{base_url}}api/Courses/GetCourseById/{{python_course_id}}
 4. Set Authorization: Bearer {{admin_token}}
 5. Click Send</t>
         </is>
@@ -2349,7 +2349,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to GET
-3. URL: {{Base_url}}api/Courses/GetAllCourses
+3. URL: {{base_url}}api/Courses/GetAllCourses
 4. Click Send</t>
         </is>
       </c>
@@ -2430,7 +2430,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to GET
-3. URL: {{Base_url}}api/Courses/GetAllCourses
+3. URL: {{base_url}}api/Courses/GetAllCourses
 4. Click Send</t>
         </is>
       </c>
@@ -2511,7 +2511,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to GET
-3. URL: {{Base_url}}api/Courses/GetAllCourses
+3. URL: {{base_url}}api/Courses/GetAllCourses
 4. Click Send</t>
         </is>
       </c>
@@ -2592,7 +2592,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to GET
-3. URL: {{Base_url}}api/Courses/GetAllCourses
+3. URL: {{base_url}}api/Courses/GetAllCourses
 4. Click Send</t>
         </is>
       </c>
@@ -2677,7 +2677,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Courses/CreateCourse
+3. URL: {{base_url}}api/Courses/CreateCourse
 4. Do NOT set Authorization header
 5. Add course data as form-data
 6. Click Send</t>
@@ -2764,7 +2764,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Courses/CreateCourse
+3. URL: {{base_url}}api/Courses/CreateCourse
 4. Do NOT set Authorization header
 5. Add course data as form-data
 6. Click Send</t>
@@ -2851,7 +2851,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Courses/CreateCourse
+3. URL: {{base_url}}api/Courses/CreateCourse
 4. Do NOT set Authorization header
 5. Add course data as form-data
 6. Click Send</t>
@@ -2938,7 +2938,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Courses/CreateCourse
+3. URL: {{base_url}}api/Courses/CreateCourse
 4. Do NOT set Authorization header
 5. Add course data as form-data
 6. Click Send</t>
@@ -3022,7 +3022,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to PATCH
-3. URL: {{Base_url}}api/Courses/UpdateCourseById/{{PythonCourse_id}}
+3. URL: {{base_url}}api/Courses/UpdateCourseById/{{python_course_id}}
 4. Set Authorization: Bearer {{admin_token}}
 5. Add patch body
 6. Click Send</t>
@@ -3106,7 +3106,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to PATCH
-3. URL: {{Base_url}}api/Courses/UpdateCourseById/{{PythonCourse_id}}
+3. URL: {{base_url}}api/Courses/UpdateCourseById/{{python_course_id}}
 4. Do NOT set Authorization header
 5. Add patch body
 6. Click Send</t>
@@ -3183,14 +3183,14 @@
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>Course ID: {{PythonCourse_id}}</t>
+          <t>Course ID: {{python_course_id}}</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
           <t>1. Open Postman
 2. Set method to DELETE
-3. URL: {{Base_url}}api/Courses/DeleteCourse/{{PythonCourse_id}}
+3. URL: {{base_url}}api/Courses/DeleteCourse/{{python_course_id}}
 4. Set Authorization: Bearer {{admin_token}}
 5. Click Send</t>
         </is>
@@ -3266,14 +3266,14 @@
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
-          <t>Course ID: {{PythonCourse_id}}</t>
+          <t>Course ID: {{python_course_id}}</t>
         </is>
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
           <t>1. Open Postman
 2. Set method to DELETE
-3. URL: {{Base_url}}api/Courses/DeleteCourse/{{PythonCourse_id}}
+3. URL: {{base_url}}api/Courses/DeleteCourse/{{python_course_id}}
 4. Set Authorization: Bearer {{admin_token}}
 5. Click Send</t>
         </is>
@@ -3349,14 +3349,14 @@
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>Course ID: {{PythonCourse_id}}</t>
+          <t>Course ID: {{python_course_id}}</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
           <t>1. Open Postman
 2. Set method to DELETE
-3. URL: {{Base_url}}api/Courses/DeleteCourse/{{PythonCourse_id}}
+3. URL: {{base_url}}api/Courses/DeleteCourse/{{python_course_id}}
 4. Set Authorization: Bearer {{admin_token}}
 5. Click Send</t>
         </is>
@@ -3432,14 +3432,14 @@
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>Course ID: {{PythonCourse_id}}</t>
+          <t>Course ID: {{python_course_id}}</t>
         </is>
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
           <t>1. Open Postman
 2. Set method to DELETE
-3. URL: {{Base_url}}api/Courses/DeleteCourse/{{PythonCourse_id}}
+3. URL: {{base_url}}api/Courses/DeleteCourse/{{python_course_id}}
 4. Do NOT set Authorization header
 5. Click Send</t>
         </is>
@@ -3515,14 +3515,14 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>Course ID: {{PythonCourse_id}}</t>
+          <t>Course ID: {{python_course_id}}</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
           <t>1. Open Postman
 2. Set method to DELETE
-3. URL: {{Base_url}}api/Courses/DeleteCourse/{{PythonCourse_id}}
+3. URL: {{base_url}}api/Courses/DeleteCourse/{{python_course_id}}
 4. Do NOT set Authorization header
 5. Click Send</t>
         </is>
@@ -3621,13 +3621,13 @@
         <is>
           <t>{
   "email": "{{random_email}}",
-  "password": "Student@1234",
-  "comparePassword": "Student@1234",
+  "password": "Test@1234",
+  "comparePassword": "Test@1234",
   "firstName": "Test",
   "lastName": "Student",
   "city": "Cairo",
   "phone": "01234567891",
-  "dadPhone": "01098765432"
+  "dadPhone": "02222222222"
 }</t>
         </is>
       </c>
@@ -3635,7 +3635,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/signUp
+3. URL: {{base_url}}api/Accounts/signUp
 4. Enter valid student data
 5. Click Send</t>
         </is>
@@ -3713,13 +3713,13 @@
         <is>
           <t>{
   "email": "{{random_email}}",
-  "password": "Student@1234",
-  "comparePassword": "Student@1234",
+  "password": "Test@1234",
+  "comparePassword": "Test@1234",
   "firstName": "Test",
   "lastName": "Student",
   "city": "Cairo",
   "phone": "01234567891",
-  "dadPhone": "01098765432"
+  "dadPhone": "02222222222"
 }</t>
         </is>
       </c>
@@ -3727,7 +3727,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/signUp
+3. URL: {{base_url}}api/Accounts/signUp
 4. Enter valid student data
 5. Click Send</t>
         </is>
@@ -3805,13 +3805,13 @@
         <is>
           <t>{
   "email": "{{random_email}}",
-  "password": "Student@1234",
-  "comparePassword": "Student@1234",
+  "password": "Test@1234",
+  "comparePassword": "Test@1234",
   "firstName": "Test",
   "lastName": "Student",
   "city": "Cairo",
   "phone": "01234567891",
-  "dadPhone": "01098765432"
+  "dadPhone": "02222222222"
 }</t>
         </is>
       </c>
@@ -3819,7 +3819,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/signUp
+3. URL: {{base_url}}api/Accounts/signUp
 4. Enter valid student data
 5. Click Send</t>
         </is>
@@ -3897,13 +3897,13 @@
         <is>
           <t>{
   "email": "{{random_email}}",
-  "password": "Student@1234",
-  "comparePassword": "Student@1234",
+  "password": "Test@1234",
+  "comparePassword": "Test@1234",
   "firstName": "Test",
   "lastName": "Student",
   "city": "Cairo",
   "phone": "01234567891",
-  "dadPhone": "01098765432"
+  "dadPhone": "02222222222"
 }</t>
         </is>
       </c>
@@ -3911,7 +3911,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/signUp
+3. URL: {{base_url}}api/Accounts/signUp
 4. Enter valid student data
 5. Click Send</t>
         </is>
@@ -3988,14 +3988,14 @@
         <is>
           <t>{
   "email": "{{Existing_Email}}",
-  "password": "Student@1234",
-  "comparePassword": "Student@1234",
+  "password": "Test@1234",
+  "comparePassword": "Test@1234",
   "firstName": "Test",
   "lastName": "Student",
   "stage": 1,
   "city": "Cairo",
   "phone": "01123456789",
-  "dadPhone": "01098765432"
+  "dadPhone": "02222222222"
 }</t>
         </is>
       </c>
@@ -4003,7 +4003,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/signUp
+3. URL: {{base_url}}api/Accounts/signUp
 4. Use already registered email
 5. Click Send</t>
         </is>
@@ -4080,14 +4080,14 @@
         <is>
           <t>{
   "email": "{{Existing_Email}}",
-  "password": "Student@1234",
-  "comparePassword": "Student@1234",
+  "password": "Test@1234",
+  "comparePassword": "Test@1234",
   "firstName": "Test",
   "lastName": "Student",
   "stage": 1,
   "city": "Cairo",
   "phone": "01123456789",
-  "dadPhone": "01098765432"
+  "dadPhone": "02222222222"
 }</t>
         </is>
       </c>
@@ -4095,7 +4095,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/signUp
+3. URL: {{base_url}}api/Accounts/signUp
 4. Use already registered email
 5. Click Send</t>
         </is>
@@ -4172,14 +4172,14 @@
         <is>
           <t>{
   "email": "{{Existing_Email}}",
-  "password": "Student@1234",
-  "comparePassword": "Student@1234",
+  "password": "Test@1234",
+  "comparePassword": "Test@1234",
   "firstName": "Test",
   "lastName": "Student",
   "stage": 1,
   "city": "Cairo",
   "phone": "01123456789",
-  "dadPhone": "01098765432"
+  "dadPhone": "02222222222"
 }</t>
         </is>
       </c>
@@ -4187,7 +4187,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/signUp
+3. URL: {{base_url}}api/Accounts/signUp
 4. Use already registered email
 5. Click Send</t>
         </is>
@@ -4264,14 +4264,14 @@
         <is>
           <t>{
   "email": "{{Existing_Email}}",
-  "password": "Student@1234",
-  "comparePassword": "Student@1234",
+  "password": "Test@1234",
+  "comparePassword": "Test@1234",
   "firstName": "Test",
   "lastName": "Student",
   "stage": 1,
   "city": "Cairo",
   "phone": "01123456789",
-  "dadPhone": "01098765432"
+  "dadPhone": "02222222222"
 }</t>
         </is>
       </c>
@@ -4279,7 +4279,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/signUp
+3. URL: {{base_url}}api/Accounts/signUp
 4. Use already registered email
 5. Click Send</t>
         </is>
@@ -4356,14 +4356,14 @@
         <is>
           <t>{
   "email": "{{invalid_email_format}}",
-  "password": "Student@1234",
-  "comparePassword": "Student@1234",
+  "password": "Test@1234",
+  "comparePassword": "Test@1234",
   "firstName": "Test",
   "lastName": "Student",
   "stage": 1,
   "city": "Cairo",
   "phone": "00000000000",
-  "dadPhone": "01098765432"
+  "dadPhone": "02222222222"
 }</t>
         </is>
       </c>
@@ -4371,7 +4371,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/signUp
+3. URL: {{base_url}}api/Accounts/signUp
 4. Enter invalid email (e.g. test@1)
 5. Click Send</t>
         </is>
@@ -4448,14 +4448,14 @@
         <is>
           <t>{
   "email": "{{invalid_email_format}}",
-  "password": "Student@1234",
-  "comparePassword": "Student@1234",
+  "password": "Test@1234",
+  "comparePassword": "Test@1234",
   "firstName": "Test",
   "lastName": "Student",
   "stage": 1,
   "city": "Cairo",
   "phone": "00000000000",
-  "dadPhone": "01098765432"
+  "dadPhone": "02222222222"
 }</t>
         </is>
       </c>
@@ -4463,7 +4463,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/signUp
+3. URL: {{base_url}}api/Accounts/signUp
 4. Enter invalid email (e.g. test@1)
 5. Click Send</t>
         </is>
@@ -4540,14 +4540,14 @@
         <is>
           <t>{
   "email": "{{invalid_email_format}}",
-  "password": "Student@1234",
-  "comparePassword": "Student@1234",
+  "password": "Test@1234",
+  "comparePassword": "Test@1234",
   "firstName": "Test",
   "lastName": "Student",
   "stage": 1,
   "city": "Cairo",
   "phone": "00000000000",
-  "dadPhone": "01098765432"
+  "dadPhone": "02222222222"
 }</t>
         </is>
       </c>
@@ -4555,7 +4555,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/signUp
+3. URL: {{base_url}}api/Accounts/signUp
 4. Enter invalid email (e.g. test@1)
 5. Click Send</t>
         </is>
@@ -4632,14 +4632,14 @@
         <is>
           <t>{
   "email": "{{random_Email}}",
-  "password": "Student@1234",
+  "password": "Test@1234",
   "comparePassword": "Stud@1234",
   "firstName": "Test",
   "lastName": "Student",
   "stage": 1,
   "city": "Cairo",
   "phone": "01234567891",
-  "dadPhone": "01098765432"
+  "dadPhone": "02222222222"
 }</t>
         </is>
       </c>
@@ -4647,7 +4647,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/signUp
+3. URL: {{base_url}}api/Accounts/signUp
 4. Set different password and comparePassword
 5. Click Send</t>
         </is>
@@ -4724,14 +4724,14 @@
         <is>
           <t>{
   "email": "{{random_Email}}",
-  "password": "Student@1234",
+  "password": "Test@1234",
   "comparePassword": "Stud@1234",
   "firstName": "Test",
   "lastName": "Student",
   "stage": 1,
   "city": "Cairo",
   "phone": "01234567891",
-  "dadPhone": "01098765432"
+  "dadPhone": "02222222222"
 }</t>
         </is>
       </c>
@@ -4739,7 +4739,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/signUp
+3. URL: {{base_url}}api/Accounts/signUp
 4. Set different password and comparePassword
 5. Click Send</t>
         </is>
@@ -4831,7 +4831,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/signUp
+3. URL: {{base_url}}api/Accounts/signUp
 4. Send body with all empty string values
 5. Click Send</t>
         </is>
@@ -4923,7 +4923,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/signUp
+3. URL: {{base_url}}api/Accounts/signUp
 4. Send body with all empty string values
 5. Click Send</t>
         </is>
@@ -5015,7 +5015,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/signUp
+3. URL: {{base_url}}api/Accounts/signUp
 4. Send body with all empty string values
 5. Click Send</t>
         </is>
@@ -5107,7 +5107,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/signUp
+3. URL: {{base_url}}api/Accounts/signUp
 4. Send body with all empty string values
 5. Click Send</t>
         </is>
@@ -5199,7 +5199,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/signUp
+3. URL: {{base_url}}api/Accounts/signUp
 4. Send body with all empty string values
 5. Click Send</t>
         </is>
@@ -5276,8 +5276,8 @@
         <is>
           <t>{
   "email": "{{invalid_email_format}}",
-  "password": "Student@1234",
-  "comparePassword": "Student@1234",
+  "password": "Test@1234",
+  "comparePassword": "Test@1234",
   "firstName": "Test",
   "lastName": "Student",
   "city": "Cairo",
@@ -5290,7 +5290,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/signUp
+3. URL: {{base_url}}api/Accounts/signUp
 4. Enter repeated zeros as phone
 5. Click Send</t>
         </is>
@@ -5367,8 +5367,8 @@
         <is>
           <t>{
   "email": "{{invalid_email_format}}",
-  "password": "Student@1234",
-  "comparePassword": "Student@1234",
+  "password": "Test@1234",
+  "comparePassword": "Test@1234",
   "firstName": "Test",
   "lastName": "Student",
   "city": "Cairo",
@@ -5381,7 +5381,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/signUp
+3. URL: {{base_url}}api/Accounts/signUp
 4. Enter repeated zeros as phone
 5. Click Send</t>
         </is>
@@ -5464,7 +5464,7 @@
   "lastName": "Student",
   "city": "Cairo",
   "phone": "01234567891",
-  "dadPhone": "01098765432"
+  "dadPhone": "02222222222"
 }</t>
         </is>
       </c>
@@ -5472,7 +5472,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/signUp
+3. URL: {{base_url}}api/Accounts/signUp
 4. Set email to null
 5. Click Send</t>
         </is>
@@ -5555,7 +5555,7 @@
   "lastName": "Student",
   "city": "Cairo",
   "phone": "01234567891",
-  "dadPhone": "01098765432"
+  "dadPhone": "02222222222"
 }</t>
         </is>
       </c>
@@ -5563,7 +5563,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/signUp
+3. URL: {{base_url}}api/Accounts/signUp
 4. Set email to null
 5. Click Send</t>
         </is>
@@ -5640,7 +5640,7 @@
         <is>
           <t>{
   "email": "{{Existing_Email}}",
-  "password": "Student@1234"
+  "password": "Test@1234"
 }</t>
         </is>
       </c>
@@ -5648,7 +5648,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/Login
+3. URL: {{base_url}}api/Accounts/Login
 4. Enter valid credentials
 5. Click Send</t>
         </is>
@@ -5725,7 +5725,7 @@
         <is>
           <t>{
   "email": "{{Existing_Email}}",
-  "password": "Student@1234"
+  "password": "Test@1234"
 }</t>
         </is>
       </c>
@@ -5733,7 +5733,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/Login
+3. URL: {{base_url}}api/Accounts/Login
 4. Enter valid credentials
 5. Click Send</t>
         </is>
@@ -5810,7 +5810,7 @@
         <is>
           <t>{
   "email": "{{Existing_Email}}",
-  "password": "Student@1234"
+  "password": "Test@1234"
 }</t>
         </is>
       </c>
@@ -5818,7 +5818,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/Login
+3. URL: {{base_url}}api/Accounts/Login
 4. Enter valid credentials
 5. Click Send</t>
         </is>
@@ -5895,7 +5895,7 @@
         <is>
           <t>{
   "email": "{{Existing_Email}}",
-  "password": "Student@1234"
+  "password": "Test@1234"
 }</t>
         </is>
       </c>
@@ -5903,7 +5903,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/Login
+3. URL: {{base_url}}api/Accounts/Login
 4. Enter valid credentials
 5. Click Send</t>
         </is>
@@ -5980,7 +5980,7 @@
         <is>
           <t>{
   "email": "{{Existing_Email}}",
-  "password": "Student@1234"
+  "password": "Test@1234"
 }</t>
         </is>
       </c>
@@ -5988,7 +5988,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/Login
+3. URL: {{base_url}}api/Accounts/Login
 4. Enter valid credentials
 5. Click Send</t>
         </is>
@@ -6065,7 +6065,7 @@
         <is>
           <t>{
   "email": "{{Existing_Email}}",
-  "password": "Student@1234"
+  "password": "Test@1234"
 }</t>
         </is>
       </c>
@@ -6073,7 +6073,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/Login
+3. URL: {{base_url}}api/Accounts/Login
 4. Enter valid credentials
 5. Click Send</t>
         </is>
@@ -6150,7 +6150,7 @@
         <is>
           <t>{
   "email": "{{Existing_Email}}",
-  "password": "Student@1234"
+  "password": "Test@1234"
 }</t>
         </is>
       </c>
@@ -6158,7 +6158,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/Login
+3. URL: {{base_url}}api/Accounts/Login
 4. Enter valid credentials
 5. Click Send</t>
         </is>
@@ -6235,7 +6235,7 @@
         <is>
           <t>{
   "email": "{{unregistered_Email}}",
-  "password": "Student@1234"
+  "password": "Test@1234"
 }</t>
         </is>
       </c>
@@ -6243,7 +6243,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/Login
+3. URL: {{base_url}}api/Accounts/Login
 4. Enter unregistered email
 5. Click Send</t>
         </is>
@@ -6320,7 +6320,7 @@
         <is>
           <t>{
   "email": "{{unregistered_Email}}",
-  "password": "Student@1234"
+  "password": "Test@1234"
 }</t>
         </is>
       </c>
@@ -6328,7 +6328,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/Login
+3. URL: {{base_url}}api/Accounts/Login
 4. Enter unregistered email
 5. Click Send</t>
         </is>
@@ -6405,7 +6405,7 @@
         <is>
           <t>{
   "email": "{{unregistered_Email}}",
-  "password": "Student@1234"
+  "password": "Test@1234"
 }</t>
         </is>
       </c>
@@ -6413,7 +6413,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/Login
+3. URL: {{base_url}}api/Accounts/Login
 4. Enter unregistered email
 5. Click Send</t>
         </is>
@@ -6490,7 +6490,7 @@
         <is>
           <t>{
   "email": "{{unverified_email}}",
-  "password": "Student@1234"
+  "password": "Test@1234"
 }</t>
         </is>
       </c>
@@ -6498,7 +6498,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/Login
+3. URL: {{base_url}}api/Accounts/Login
 4. Enter unverified email credentials
 5. Click Send</t>
         </is>
@@ -6575,7 +6575,7 @@
         <is>
           <t>{
   "email": "{{unverified_email}}",
-  "password": "Student@1234"
+  "password": "Test@1234"
 }</t>
         </is>
       </c>
@@ -6583,7 +6583,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/Login
+3. URL: {{base_url}}api/Accounts/Login
 4. Enter unverified email credentials
 5. Click Send</t>
         </is>
@@ -6668,7 +6668,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/Login
+3. URL: {{base_url}}api/Accounts/Login
 4. Enter valid email with wrong password
 5. Click Send</t>
         </is>
@@ -6753,7 +6753,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/Login
+3. URL: {{base_url}}api/Accounts/Login
 4. Enter valid email with wrong password
 5. Click Send</t>
         </is>
@@ -6838,7 +6838,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/Login
+3. URL: {{base_url}}api/Accounts/Login
 4. Enter valid email with wrong password
 5. Click Send</t>
         </is>
@@ -6908,14 +6908,14 @@
       <c r="F74" s="14" t="inlineStr">
         <is>
           <t>1. Server running
-2. omar@student.com is blocked in the system</t>
+2. student@example.com is blocked in the system</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
         <is>
           <t>{
-  "email": "omar@student.com",
-  "password": "Student@1234"
+  "email": "student@example.com",
+  "password": "Test@1234"
 }</t>
         </is>
       </c>
@@ -6923,7 +6923,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/Login
+3. URL: {{base_url}}api/Accounts/Login
 4. Enter blocked user credentials
 5. Click Send</t>
         </is>
@@ -6993,14 +6993,14 @@
       <c r="F75" s="7" t="inlineStr">
         <is>
           <t>1. Server running
-2. omar@student.com is blocked in the system</t>
+2. student@example.com is blocked in the system</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
           <t>{
-  "email": "omar@student.com",
-  "password": "Student@1234"
+  "email": "student@example.com",
+  "password": "Test@1234"
 }</t>
         </is>
       </c>
@@ -7008,7 +7008,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/Login
+3. URL: {{base_url}}api/Accounts/Login
 4. Enter blocked user credentials
 5. Click Send</t>
         </is>
@@ -7078,14 +7078,14 @@
       <c r="F76" s="14" t="inlineStr">
         <is>
           <t>1. Server running
-2. omar@student.com is blocked in the system</t>
+2. student@example.com is blocked in the system</t>
         </is>
       </c>
       <c r="G76" s="14" t="inlineStr">
         <is>
           <t>{
-  "email": "omar@student.com",
-  "password": "Student@1234"
+  "email": "student@example.com",
+  "password": "Test@1234"
 }</t>
         </is>
       </c>
@@ -7093,7 +7093,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/Login
+3. URL: {{base_url}}api/Accounts/Login
 4. Enter blocked user credentials
 5. Click Send</t>
         </is>
@@ -7174,7 +7174,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/Login
+3. URL: {{base_url}}api/Accounts/Login
 4. Send empty body
 5. Click Send</t>
         </is>
@@ -7255,7 +7255,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/Login
+3. URL: {{base_url}}api/Accounts/Login
 4. Send empty body
 5. Click Send</t>
         </is>
@@ -7331,7 +7331,7 @@
         <is>
           <t>{
   "email": "omar@1",
-  "password": "Student@1234"
+  "password": "Test@1234"
 }</t>
         </is>
       </c>
@@ -7339,7 +7339,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/Login
+3. URL: {{base_url}}api/Accounts/Login
 4. Enter invalid email format
 5. Click Send</t>
         </is>
@@ -7415,7 +7415,7 @@
         <is>
           <t>{
   "email": "omar@1",
-  "password": "Student@1234"
+  "password": "Test@1234"
 }</t>
         </is>
       </c>
@@ -7423,7 +7423,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/Login
+3. URL: {{base_url}}api/Accounts/Login
 4. Enter invalid email format
 5. Click Send</t>
         </is>
@@ -7527,7 +7527,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/SendCode?email=rihijo6869@deapad.com
+3. URL: {{base_url}}api/Accounts/SendCode?email=rihijo6869@deapad.com
 4. No body required
 5. Click Send</t>
         </is>
@@ -7610,7 +7610,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/SendCode?email=rihijo6869@deapad.com
+3. URL: {{base_url}}api/Accounts/SendCode?email=rihijo6869@deapad.com
 4. No body required
 5. Click Send</t>
         </is>
@@ -7693,7 +7693,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/SendCode?email=rihijo6869@deapad.com
+3. URL: {{base_url}}api/Accounts/SendCode?email=rihijo6869@deapad.com
 4. No body required
 5. Click Send</t>
         </is>
@@ -7776,7 +7776,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/SendCode?email=rihijo6869@deapad.com
+3. URL: {{base_url}}api/Accounts/SendCode?email=rihijo6869@deapad.com
 4. No body required
 5. Click Send</t>
         </is>
@@ -8189,7 +8189,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/ValidateCode?email=fayosi4973@deapad.com&amp;code=561590&amp;isForResetPassword=false
+3. URL: {{base_url}}api/Accounts/ValidateCode?email=fayosi4973@deapad.com&amp;code=561590&amp;isForResetPassword=false
 4. Click Send</t>
         </is>
       </c>
@@ -8273,7 +8273,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/ValidateCode?email=fayosi4973@deapad.com&amp;code=561590&amp;isForResetPassword=false
+3. URL: {{base_url}}api/Accounts/ValidateCode?email=fayosi4973@deapad.com&amp;code=561590&amp;isForResetPassword=false
 4. Click Send</t>
         </is>
       </c>
@@ -8357,7 +8357,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/ValidateCode?email=rihijo6869@deapad.com&amp;code=560467&amp;isForResetPassword=false
+3. URL: {{base_url}}api/Accounts/ValidateCode?email=rihijo6869@deapad.com&amp;code=560467&amp;isForResetPassword=false
 4. Click Send</t>
         </is>
       </c>
@@ -8441,7 +8441,7 @@
         <is>
           <t>1. Open Postman
 2. Set method to POST
-3. URL: {{Base_url}}api/Accounts/ValidateCode?email=rihijo6869@deapad.com&amp;code=560467&amp;isForResetPassword=false
+3. URL: {{base_url}}api/Accounts/ValidateCode?email=rihijo6869@deapad.com&amp;code=560467&amp;isForResetPassword=false
 4. Click Send</t>
         </is>
       </c>
